--- a/artfynd/A 24140-2022 artfynd.xlsx
+++ b/artfynd/A 24140-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137176882</v>
       </c>
       <c r="B2" t="n">
-        <v>83354</v>
+        <v>83356</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137176861</v>
       </c>
       <c r="B4" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 24140-2022 artfynd.xlsx
+++ b/artfynd/A 24140-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137176882</v>
       </c>
       <c r="B2" t="n">
-        <v>83356</v>
+        <v>83369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137176885</v>
       </c>
       <c r="B3" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137176861</v>
       </c>
       <c r="B4" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 24140-2022 artfynd.xlsx
+++ b/artfynd/A 24140-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137176882</v>
       </c>
       <c r="B2" t="n">
-        <v>83369</v>
+        <v>83371</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137176885</v>
       </c>
       <c r="B3" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137176861</v>
       </c>
       <c r="B4" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 24140-2022 artfynd.xlsx
+++ b/artfynd/A 24140-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137176882</v>
       </c>
       <c r="B2" t="n">
-        <v>83371</v>
+        <v>83381</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137176885</v>
       </c>
       <c r="B3" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137176861</v>
       </c>
       <c r="B4" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 24140-2022 artfynd.xlsx
+++ b/artfynd/A 24140-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137176882</v>
       </c>
       <c r="B2" t="n">
-        <v>83381</v>
+        <v>83384</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137176885</v>
       </c>
       <c r="B3" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137176861</v>
       </c>
       <c r="B4" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 24140-2022 artfynd.xlsx
+++ b/artfynd/A 24140-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137176882</v>
       </c>
       <c r="B2" t="n">
-        <v>83384</v>
+        <v>83389</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137176885</v>
       </c>
       <c r="B3" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137176861</v>
       </c>
       <c r="B4" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 24140-2022 artfynd.xlsx
+++ b/artfynd/A 24140-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137176882</v>
       </c>
       <c r="B2" t="n">
-        <v>83389</v>
+        <v>83400</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137176861</v>
       </c>
       <c r="B4" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 24140-2022 artfynd.xlsx
+++ b/artfynd/A 24140-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137176882</v>
       </c>
       <c r="B2" t="n">
-        <v>83400</v>
+        <v>83401</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137176861</v>
       </c>
       <c r="B4" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 24140-2022 artfynd.xlsx
+++ b/artfynd/A 24140-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137176882</v>
       </c>
       <c r="B2" t="n">
-        <v>83401</v>
+        <v>83403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137176861</v>
       </c>
       <c r="B4" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 24140-2022 artfynd.xlsx
+++ b/artfynd/A 24140-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137176882</v>
       </c>
       <c r="B2" t="n">
-        <v>83403</v>
+        <v>83407</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137176885</v>
       </c>
       <c r="B3" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137176861</v>
       </c>
       <c r="B4" t="n">
-        <v>79293</v>
+        <v>79297</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
